--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.2183</v>
+        <v>17.73123</v>
       </c>
       <c r="D2" t="n">
-        <v>17.65576</v>
+        <v>17.27267</v>
       </c>
       <c r="E2" t="n">
-        <v>17.34003</v>
+        <v>17.58532</v>
       </c>
       <c r="F2" t="n">
-        <v>44.9721</v>
+        <v>45.17077</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05324</v>
+        <v>0.05258</v>
       </c>
       <c r="H2" t="n">
-        <v>1.91046</v>
+        <v>1.90805</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.65471</v>
+        <v>17.71369</v>
       </c>
       <c r="D3" t="n">
-        <v>17.34683</v>
+        <v>17.0305</v>
       </c>
       <c r="E3" t="n">
-        <v>17.52683</v>
+        <v>17.62071</v>
       </c>
       <c r="F3" t="n">
-        <v>43.61839</v>
+        <v>43.95633</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05318</v>
+        <v>0.05326</v>
       </c>
       <c r="H3" t="n">
-        <v>1.90334</v>
+        <v>1.929</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.87925</v>
+        <v>17.3786</v>
       </c>
       <c r="D4" t="n">
-        <v>17.28412</v>
+        <v>17.28618</v>
       </c>
       <c r="E4" t="n">
-        <v>17.79854</v>
+        <v>17.37084</v>
       </c>
       <c r="F4" t="n">
-        <v>45.63059</v>
+        <v>44.85705</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05435</v>
+        <v>0.05304</v>
       </c>
       <c r="H4" t="n">
-        <v>1.93211</v>
+        <v>1.93901</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.52994</v>
+        <v>17.18717</v>
       </c>
       <c r="D6" t="n">
-        <v>16.82411</v>
+        <v>16.76897</v>
       </c>
       <c r="E6" t="n">
-        <v>17.3177</v>
+        <v>17.18689</v>
       </c>
       <c r="F6" t="n">
-        <v>22.59124</v>
+        <v>22.49955</v>
       </c>
       <c r="G6" t="n">
-        <v>36.32037</v>
+        <v>36.08997</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.52596</v>
+        <v>17.25239</v>
       </c>
       <c r="D7" t="n">
-        <v>16.69396</v>
+        <v>16.75671</v>
       </c>
       <c r="E7" t="n">
-        <v>17.2747</v>
+        <v>17.18798</v>
       </c>
       <c r="F7" t="n">
-        <v>22.87261</v>
+        <v>22.85606</v>
       </c>
       <c r="G7" t="n">
-        <v>35.0468</v>
+        <v>36.53984</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.8241</v>
+        <v>17.49791</v>
       </c>
       <c r="D8" t="n">
-        <v>16.43162</v>
+        <v>16.70985</v>
       </c>
       <c r="E8" t="n">
-        <v>17.21664</v>
+        <v>17.24085</v>
       </c>
       <c r="F8" t="n">
-        <v>22.87639</v>
+        <v>23.07303</v>
       </c>
       <c r="G8" t="n">
-        <v>35.85808</v>
+        <v>35.49067</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.63247</v>
+        <v>0.63401</v>
       </c>
       <c r="D10" t="n">
-        <v>1.16949</v>
+        <v>1.18312</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6276</v>
+        <v>0.63957</v>
       </c>
       <c r="D11" t="n">
-        <v>1.16702</v>
+        <v>1.177</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6319</v>
+        <v>0.63303</v>
       </c>
       <c r="D12" t="n">
-        <v>1.16859</v>
+        <v>1.15392</v>
       </c>
     </row>
   </sheetData>
